--- a/scripts/output/merged_data_6803382.xlsx
+++ b/scripts/output/merged_data_6803382.xlsx
@@ -1004,22 +1004,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pendampingan Penerapan E-Learning Interaktif Untuk Meningkatkan Literasi Digital Guru Dan Siswa Di SMA Negeri 1 Susukan</t>
+          <t>A Prediksi Prestasi Siswa Menggunakan Algoritma Decision Tree C4. 5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Pendampingan Penerapan E-Learning Interaktif Untuk Meningkatkan Literasi Digital Guru Dan Siswa Di SMA Negeri 1 Susukan'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'A Prediksi Prestasi Siswa Menggunakan Algoritma Decision Tree C4. 5'</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>S Mujiyono, A Rohman, A Pratama, UP Sanjaya, E Suryani</t>
+          <t>U Halimatussa'diyah, A Rohman</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jurnal Masyarakat Madani Indonesia 5 (1), 329-335, 2026</t>
+          <t>Jurnal Algoritma 23 (1), 51–58-51–58, 2026</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1035,22 +1035,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Penerapan Algoritma C4. 5 dalam Memprediksi Kepuasan Siswa Terhadap Kinerja Guru SMK</t>
+          <t>Jaringan Nirkabel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penerapan Algoritma C4. 5 dalam Memprediksi Kepuasan Siswa Terhadap Kinerja Guru SMK'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Jaringan Nirkabel'</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FN Anifah, A Rohman</t>
+          <t>A Rohman, D Rohmaniyah, S Renaisance, MGN Musyafa</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jurnal Algoritma 23 (1), 372–379-372–379, 2026</t>
+          <t>https://unwpress.unw.ac.id/index.php/unwpress/catalog/book/131 1, 88, 2026</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1066,22 +1066,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pendampingan Penerapan E-Learning Interaktif Untuk Meningkatkan Literasi Digital Guru Dan Siswa Di SMA Negeri 1 Susukan</t>
+          <t>IMPLEMENTASI SIMPLE ADDITIVE WEIGHTING (SAW) DALAM SISTEM PENDUKUNG KEPUTUSAN PEMILIHAN GURU BERPRESTASI DI SMK NU UNGARAN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Pendampingan Penerapan E-Learning Interaktif Untuk Meningkatkan Literasi Digital Guru Dan Siswa Di SMA Negeri 1 Susukan'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'IMPLEMENTASI SIMPLE ADDITIVE WEIGHTING (SAW) DALAM SISTEM PENDUKUNG KEPUTUSAN PEMILIHAN GURU BERPRESTASI DI SMK NU UNGARAN'</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>S Mujiyono, A Rohman, A Pratama, UP Sanjaya, E Suryani</t>
+          <t>R Rohamini, SI Novichasar, A Rohman</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jurnal Masyarakat Madani Indonesia 5 (1), 329-335, 2026</t>
+          <t>Biner Jurnal Ilmiah Informatika 5 (1), 23-30, 2026</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1097,22 +1097,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jaringan Nirkabel</t>
+          <t>IMPLEMENTASI SIMPLE ADDITIVE WEIGHTING (SAW) DALAM SISTEM PENDUKUNG KEPUTUSAN PEMILIHAN GURU BERPRESTASI DI SMK NU UNGARAN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Jaringan Nirkabel'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'IMPLEMENTASI SIMPLE ADDITIVE WEIGHTING (SAW) DALAM SISTEM PENDUKUNG KEPUTUSAN PEMILIHAN GURU BERPRESTASI DI SMK NU UNGARAN'</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A Rohman, D Rohmaniyah, S Renaisance, MGN Musyafa</t>
+          <t>R Rohamini, SI Novichasar, A Rohman</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://unwpress.unw.ac.id/index.php/unwpress/catalog/book/131 1, 88, 2026</t>
+          <t>Biner Jurnal Ilmiah Informatika 5 (1), 23-30, 2026</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1128,22 +1128,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sistem Pakar Diagnosa Penyakit Pernapasan Menggunakan Metode Naive Bayes Berbasis Web</t>
+          <t>Penerapan Algoritma C4. 5 dalam Memprediksi Kepuasan Siswa Terhadap Kinerja Guru SMK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Sistem Pakar Diagnosa Penyakit Pernapasan Menggunakan Metode Naive Bayes Berbasis Web'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penerapan Algoritma C4. 5 dalam Memprediksi Kepuasan Siswa Terhadap Kinerja Guru SMK'</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CA Putri, IS Wibisono, A Rohman</t>
+          <t>FN Anifah, A Rohman</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jurnal Mahasiswa Teknik Informatika 5 (1), 456-463, 2026</t>
+          <t>Jurnal Algoritma 23 (1), 372–379-372–379, 2026</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1159,22 +1159,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jaringan Nirkabel</t>
+          <t>Sistem Pakar Diagnosa Penyakit Pernapasan Menggunakan Metode Naive Bayes Berbasis Web</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Jaringan Nirkabel'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Sistem Pakar Diagnosa Penyakit Pernapasan Menggunakan Metode Naive Bayes Berbasis Web'</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A Rohman, D Rohmaniyah, S Renaisance, MGN Musyafa</t>
+          <t>CA Putri, IS Wibisono, A Rohman</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://unwpress.unw.ac.id/index.php/unwpress/catalog/book/131 1, 88, 2026</t>
+          <t>Jurnal Mahasiswa Teknik Informatika 5 (1), 456-463, 2026</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1190,22 +1190,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A Prediksi Prestasi Siswa Menggunakan Algoritma Decision Tree C4. 5</t>
+          <t>Pendampingan Penerapan E-Learning Interaktif Untuk Meningkatkan Literasi Digital Guru Dan Siswa Di SMA Negeri 1 Susukan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'A Prediksi Prestasi Siswa Menggunakan Algoritma Decision Tree C4. 5'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Pendampingan Penerapan E-Learning Interaktif Untuk Meningkatkan Literasi Digital Guru Dan Siswa Di SMA Negeri 1 Susukan'</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>U Halimatussa'diyah, A Rohman</t>
+          <t>S Mujiyono, A Rohman, A Pratama, UP Sanjaya, E Suryani</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jurnal Algoritma 23 (1), 51–58-51–58, 2026</t>
+          <t>Jurnal Masyarakat Madani Indonesia 5 (1), 329-335, 2026</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1221,22 +1221,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IMPLEMENTASI SIMPLE ADDITIVE WEIGHTING (SAW) DALAM SISTEM PENDUKUNG KEPUTUSAN PEMILIHAN GURU BERPRESTASI DI SMK NU UNGARAN</t>
+          <t>Pendampingan Penerapan E-Learning Interaktif Untuk Meningkatkan Literasi Digital Guru Dan Siswa Di SMA Negeri 1 Susukan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'IMPLEMENTASI SIMPLE ADDITIVE WEIGHTING (SAW) DALAM SISTEM PENDUKUNG KEPUTUSAN PEMILIHAN GURU BERPRESTASI DI SMK NU UNGARAN'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Pendampingan Penerapan E-Learning Interaktif Untuk Meningkatkan Literasi Digital Guru Dan Siswa Di SMA Negeri 1 Susukan'</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>R Rohamini, SI Novichasar, A Rohman</t>
+          <t>S Mujiyono, A Rohman, A Pratama, UP Sanjaya, E Suryani</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Biner Jurnal Ilmiah Informatika 5 (1), 23-30, 2026</t>
+          <t>Jurnal Masyarakat Madani Indonesia 5 (1), 329-335, 2026</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1252,22 +1252,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IMPLEMENTASI SIMPLE ADDITIVE WEIGHTING (SAW) DALAM SISTEM PENDUKUNG KEPUTUSAN PEMILIHAN GURU BERPRESTASI DI SMK NU UNGARAN</t>
+          <t>Jaringan Nirkabel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'IMPLEMENTASI SIMPLE ADDITIVE WEIGHTING (SAW) DALAM SISTEM PENDUKUNG KEPUTUSAN PEMILIHAN GURU BERPRESTASI DI SMK NU UNGARAN'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Jaringan Nirkabel'</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>R Rohamini, SI Novichasar, A Rohman</t>
+          <t>A Rohman, D Rohmaniyah, S Renaisance, MGN Musyafa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Biner Jurnal Ilmiah Informatika 5 (1), 23-30, 2026</t>
+          <t>https://unwpress.unw.ac.id/index.php/unwpress/catalog/book/131 1, 88, 2026</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1283,29 +1283,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>APPLICATION OF WATERFALL METHOD IN SALES SYSTEM USING LARAVEL 10 FRAMEWORK IN BELLA GROCERY STORE</t>
+          <t>Optimalisasi Keterampilan Aplikasi Pengolah Kata dalam Pengembangan Kepenulisan Siswa SMK Negeri 1 Arosbaya</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'APPLICATION OF WATERFALL METHOD IN SALES SYSTEM USING LARAVEL 10 FRAMEWORK IN BELLA GROCERY STORE'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Optimalisasi Keterampilan Aplikasi Pengolah Kata dalam Pengembangan Kepenulisan Siswa SMK Negeri 1 Arosbaya'</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BDWIP FERNANDA, R ABDUL</t>
+          <t>A Rohman, N Ningsih, R Soleha, A Ilma, SK Dewi, D Fatma, AT Ni'mah</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JURNAL INOVTEK POLBENG SERI INFORMATIKA ??????????: Politeknik Negeri …, 2025</t>
+          <t>Jurnal Pemberdayaan Masyarakat dan Komunitas 2 (1), 13-21, 2025</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2025</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2334,22 +2334,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Prediksi predikat kelulusan mahasiswa menggunakan naive bayes dan decision tree</t>
+          <t>Data mining: algoritma C4.5 dan implementasi dengan rapidminer dan codeigniter</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BUKU MONOGRAF</t>
+          <t>BUKU AJAR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Agung Wibowo, Abdul Rohman</t>
+          <t>Abdul Rohman, Agung Wibowo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CV. Penerbit Lakeisha</t>
+          <t>CV Beranda Ilmu</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2357,32 +2357,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klaten</t>
+          <t>Semarang</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9786234208191</v>
+        <v>9786230970757</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Implementasi Metode Certainty Factor pada Sistem Pakar Diagnosis Penyakit Anak</t>
+          <t>Implementasi metode forward chaining dalam sistem pakar pendeteksi gangguan autism pada anak</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BUKU REFERENSI</t>
+          <t>BUKU MONOGRAF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ansatul Azzizah, Abdul Rohman, Editor: Anni Malihatul Hawa dan Ela Suryani</t>
+          <t>penulis, Sri Mujiyono, Ita Adhawiyah, Abdul Rohman</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Beranda Ilmu</t>
+          <t>CV. Penerbit Lakeisha</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2390,32 +2390,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Semarang</t>
+          <t>Ungaran</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9786230946813</v>
+        <v>9786234206265</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data mining: algoritma C4.5 dan implementasi dengan rapidminer dan codeigniter</t>
+          <t>Mudahnya membuat web e-learning berbasis web dan Android</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BUKU AJAR</t>
+          <t>BUKU REFERENSI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Abdul Rohman, Agung Wibowo</t>
+          <t>Abdul Rohman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CV Beranda Ilmu</t>
+          <t>Elex Media Komputindo</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Semarang</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9786230970757</v>
+        <v>9786230047930</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Implementasi metode forward chaining dalam sistem pakar pendeteksi gangguan autism pada anak</t>
+          <t>Pengantar Teknologi Informasi : Penulisan Dkumen ilmiah menggunakan Microsoft Word</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BUKU MONOGRAF</t>
+          <t>BUKU AJAR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>penulis, Sri Mujiyono, Ita Adhawiyah, Abdul Rohman</t>
+          <t>Abdul Rohman, Editor; Anni Malihatul Hawa dan Ela Suryani</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CV. Penerbit Lakeisha</t>
+          <t>Beranda Ilmu</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2460,28 +2460,28 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9786234206265</v>
+        <v>9786230942181</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mudahnya membuat web e-learning berbasis web dan Android</t>
+          <t>Prediksi predikat kelulusan mahasiswa menggunakan naive bayes dan decision tree</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BUKU REFERENSI</t>
+          <t>BUKU MONOGRAF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Abdul Rohman</t>
+          <t>Agung Wibowo, Abdul Rohman</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Elex Media Komputindo</t>
+          <t>CV. Penerbit Lakeisha</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2489,27 +2489,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jakarta</t>
+          <t>Klaten</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>9786230047930</v>
+        <v>9786234208191</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pengantar Teknologi Informasi : Penulisan Dkumen ilmiah menggunakan Microsoft Word</t>
+          <t>Implementasi Metode Certainty Factor pada Sistem Pakar Diagnosis Penyakit Anak</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BUKU AJAR</t>
+          <t>BUKU REFERENSI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Abdul Rohman, Editor; Anni Malihatul Hawa dan Ela Suryani</t>
+          <t>Ansatul Azzizah, Abdul Rohman, Editor: Anni Malihatul Hawa dan Ela Suryani</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2522,32 +2522,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ungaran</t>
+          <t>Semarang</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>9786230942181</v>
+        <v>9786230946813</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Monograf prediksi penyakit jantung menggunakan algoritma C4.5 berbasis Adaboost</t>
+          <t>Penerapan algoritma C4.5 untuk prediksi kepuasan mahasiswa tahun 2020</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BUKU MONOGRAF</t>
+          <t>BUKU AJAR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Abdul Rohman</t>
+          <t>Anief Rufiyanto, Muhammad Rochcham, Abdul Rohman</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CV. Penerbit Lakeisha</t>
+          <t>Deepublish</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9786234200041</v>
+        <v>9786230222023</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/output/merged_data_6803382.xlsx
+++ b/scripts/output/merged_data_6803382.xlsx
@@ -1004,22 +1004,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A Prediksi Prestasi Siswa Menggunakan Algoritma Decision Tree C4. 5</t>
+          <t>Jaringan Nirkabel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'A Prediksi Prestasi Siswa Menggunakan Algoritma Decision Tree C4. 5'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Jaringan Nirkabel'</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>U Halimatussa'diyah, A Rohman</t>
+          <t>A Rohman, D Rohmaniyah, S Renaisance, MGN Musyafa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jurnal Algoritma 23 (1), 51–58-51–58, 2026</t>
+          <t>https://unwpress.unw.ac.id/index.php/unwpress/catalog/book/131 1, 88, 2026</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1035,22 +1035,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jaringan Nirkabel</t>
+          <t>Penerapan Algoritma C4. 5 dalam Memprediksi Kepuasan Siswa Terhadap Kinerja Guru SMK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Jaringan Nirkabel'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penerapan Algoritma C4. 5 dalam Memprediksi Kepuasan Siswa Terhadap Kinerja Guru SMK'</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A Rohman, D Rohmaniyah, S Renaisance, MGN Musyafa</t>
+          <t>FN Anifah, A Rohman</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://unwpress.unw.ac.id/index.php/unwpress/catalog/book/131 1, 88, 2026</t>
+          <t>Jurnal Algoritma 23 (1), 372–379-372–379, 2026</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1128,22 +1128,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Penerapan Algoritma C4. 5 dalam Memprediksi Kepuasan Siswa Terhadap Kinerja Guru SMK</t>
+          <t>Sistem Pakar Diagnosa Penyakit Pernapasan Menggunakan Metode Naive Bayes Berbasis Web</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penerapan Algoritma C4. 5 dalam Memprediksi Kepuasan Siswa Terhadap Kinerja Guru SMK'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Sistem Pakar Diagnosa Penyakit Pernapasan Menggunakan Metode Naive Bayes Berbasis Web'</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FN Anifah, A Rohman</t>
+          <t>CA Putri, IS Wibisono, A Rohman</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jurnal Algoritma 23 (1), 372–379-372–379, 2026</t>
+          <t>Jurnal Mahasiswa Teknik Informatika 5 (1), 456-463, 2026</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1159,22 +1159,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistem Pakar Diagnosa Penyakit Pernapasan Menggunakan Metode Naive Bayes Berbasis Web</t>
+          <t>A Prediksi Prestasi Siswa Menggunakan Algoritma Decision Tree C4. 5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Sistem Pakar Diagnosa Penyakit Pernapasan Menggunakan Metode Naive Bayes Berbasis Web'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'A Prediksi Prestasi Siswa Menggunakan Algoritma Decision Tree C4. 5'</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CA Putri, IS Wibisono, A Rohman</t>
+          <t>U Halimatussa'diyah, A Rohman</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jurnal Mahasiswa Teknik Informatika 5 (1), 456-463, 2026</t>
+          <t>Jurnal Algoritma 23 (1), 51–58-51–58, 2026</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1283,29 +1283,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optimalisasi Keterampilan Aplikasi Pengolah Kata dalam Pengembangan Kepenulisan Siswa SMK Negeri 1 Arosbaya</t>
+          <t>Cara Praktis Dan Gratis Membuat Website Sekolah</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Optimalisasi Keterampilan Aplikasi Pengolah Kata dalam Pengembangan Kepenulisan Siswa SMK Negeri 1 Arosbaya'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Cara Praktis Dan Gratis Membuat Website Sekolah'</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A Rohman, N Ningsih, R Soleha, A Ilma, SK Dewi, D Fatma, AT Ni'mah</t>
+          <t>A Rohman</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jurnal Pemberdayaan Masyarakat dan Komunitas 2 (1), 13-21, 2025</t>
+          <t>Elex Media Komputindo, 2025</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2025</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
